--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="B127" s="39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
-          <t>10/1 · 10/2 팀 결정 반영 — 담당 변경(공통 수인 · RAG 채연), REQ-049 다제약물 5개 확정, 임부금기 MVP 제외 표시, NFR-023 내비(홈 상단 · 나머지 하단 · 챗봇 플로팅), 챗봇 PR #3 반영(REQ-073 · 076 확정, 신규 REQ-102 · 130 · 131 · 132), API 명세서 v1.3 · ERD v1.3 참조 / 10/6 회의 결정 반영 — MVP 확정, 회원 · 개인정보 기준 5개(파기 범위 · 로그아웃 제외 · 원본 사진 즉시 삭제 · 동의 없는 챗봇 신규 REQ-133 · 의료 표현 목록), 로그인 유지 60분 · 14일, 안전성 30일 기준 병용금기 · 효능군 확대, 챌린지 기준(성규 인수인계) 반영, 챌린지 담당 변경</t>
+          <t>10/1 · 10/2 팀 결정 반영 — 담당 변경(공통 수인 · RAG 채연), REQ-049 다제약물 5개 확정, 임부금기 MVP 제외 표시, NFR-023 내비(홈 상단 · 나머지 하단 · 챗봇 플로팅), 챗봇 PR #3 반영(REQ-073 · 076 확정, 신규 REQ-102 · 130 · 131 · 132), API 명세서 v1.3 · ERD v1.3 참조 / 10/6 회의 결정 반영 — MVP 확정, 회원 · 개인정보 기준 5개(파기 범위 · 로그아웃 제외 · 원본 사진 즉시 삭제 · 동의 없는 챗봇 신규 REQ-133 · 의료 표현 목록), 로그인 유지 60분 · 14일, 안전성 30일 기준 병용금기 · 효능군 확대, 챌린지 기준(성규 인수인계) 반영, 챌린지 담당 변경, REQ-132 시간 초과 30초 확정</t>
         </is>
       </c>
       <c r="D127" s="43" t="n"/>
@@ -4468,6 +4468,25 @@
         </is>
       </c>
       <c r="E180" s="42" t="n"/>
+    </row>
+    <row r="181" hidden="1" outlineLevel="1">
+      <c r="A181" s="42" t="n"/>
+      <c r="B181" s="42" t="inlineStr">
+        <is>
+          <t>챗봇 / REQ-132 답변 오류 처리 / 비고</t>
+        </is>
+      </c>
+      <c r="C181" s="42" t="inlineStr">
+        <is>
+          <t>시간 초과 기준은 임시 30초, arq 작업 제한 시간과 맞춰 확정 (설계 메모 4-7)</t>
+        </is>
+      </c>
+      <c r="D181" s="42" t="inlineStr">
+        <is>
+          <t>시간 초과 기준 30초 확정 · 챗봇 작업(arq) 제한 25초 · 워커 전체 60초는 그대로 (10/6 수인 #52, 설계 메모 4-7)</t>
+        </is>
+      </c>
+      <c r="E181" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -10711,7 +10730,7 @@
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>시간 초과 기준은 임시 30초, arq 작업 제한 시간과 맞춰 확정 (설계 메모 4-7)</t>
+          <t>시간 초과 기준 30초 확정 · 챗봇 작업(arq) 제한 25초 · 워커 전체 60초는 그대로 (10/6 수인 #52, 설계 메모 4-7)</t>
         </is>
       </c>
       <c r="N18" s="48" t="inlineStr">

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C127" s="40" t="inlineStr">
         <is>
-          <t>10/1 · 10/2 팀 결정 반영 — 담당 변경(공통 수인 · RAG 채연), REQ-049 다제약물 5개 확정, 임부금기 MVP 제외 표시, NFR-023 내비(홈 상단 · 나머지 하단 · 챗봇 플로팅), 챗봇 PR #3 반영(REQ-073 · 076 확정, 신규 REQ-102 · 130 · 131 · 132), API 명세서 v1.3 · ERD v1.3 참조 / 10/6 회의 결정 반영 — MVP 확정, 회원 · 개인정보 기준 5개(파기 범위 · 로그아웃 제외 · 원본 사진 즉시 삭제 · 동의 없는 챗봇 신규 REQ-133 · 의료 표현 목록), 로그인 유지 60분 · 14일, 안전성 30일 기준 병용금기 · 효능군 확대, 챌린지 기준(성규 인수인계) 반영, 챌린지 담당 변경, REQ-132 시간 초과 30초 확정</t>
+          <t>10/1 · 10/2 팀 결정 반영 — 담당 변경(공통 수인 · RAG 채연), REQ-049 다제약물 5개 확정, 임부금기 MVP 제외 표시, NFR-023 내비(홈 상단 · 나머지 하단 · 챗봇 플로팅), 챗봇 PR #3 반영(REQ-073 · 076 확정, 신규 REQ-102 · 130 · 131 · 132), API 명세서 v1.3 · ERD v1.3 참조 / 10/6 회의 결정 반영 — MVP 확정, 회원 · 개인정보 기준 5개(파기 범위 · 로그아웃 제외 · 원본 사진 즉시 삭제 · 동의 없는 챗봇 신규 REQ-133 · 의료 표현 목록), 로그인 유지 60분 · 14일, 안전성 30일 기준 병용금기 · 효능군 확대, 챌린지 기준(성규 인수인계) 반영, 챌린지 담당 변경, REQ-132 시간 초과 30초 확정 / 챗봇 음성 질문(REQ-078)을 키보드 받아쓰기로 변경 (CB-05-E1 · CB-05-P · CB-05-E2 삭제, 화면 53개 → 50개, 수인 #50)</t>
         </is>
       </c>
       <c r="D127" s="43" t="n"/>
@@ -4487,6 +4487,64 @@
         </is>
       </c>
       <c r="E181" s="42" t="n"/>
+    </row>
+    <row r="182" hidden="1" outlineLevel="1">
+      <c r="A182" s="42" t="n"/>
+      <c r="B182" s="42" t="inlineStr">
+        <is>
+          <t>챗봇 / REQ-078 음성 질문 입력 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C182" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 말로 질문을 입력할 수 있어야 하며, 인식에 실패하면 다시 말하기 또는 글자 입력을 선택할 수 있다.</t>
+        </is>
+      </c>
+      <c r="D182" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 키보드 받아쓰기로 말로 질문을 입력할 수 있고, 처음 몇 번은 사용 방법을 안내받는다.
+사유: 앱이 직접 녹음하지 않고 키보드의 받아쓰기를 쓰도록 안내하는 방식으로 확정 (10/6 수인 #50, 설계 메모 4-10)</t>
+        </is>
+      </c>
+      <c r="E182" s="42" t="n"/>
+    </row>
+    <row r="183" hidden="1" outlineLevel="1">
+      <c r="A183" s="42" t="n"/>
+      <c r="B183" s="42" t="inlineStr">
+        <is>
+          <t>챗봇 / REQ-078 음성 질문 입력 / 관련 화면</t>
+        </is>
+      </c>
+      <c r="C183" s="42" t="inlineStr">
+        <is>
+          <t>CB-05 · CB-05-E1</t>
+        </is>
+      </c>
+      <c r="D183" s="42" t="inlineStr">
+        <is>
+          <t>CB-05 (받아쓰기 안내) — 마이크 권한을 쓰지 않아 CB-05-P · CB-05-E2 삭제, 인식은 키보드가 해서 앱이 실패를 알 수 없어 CB-05-E1도 삭제</t>
+        </is>
+      </c>
+      <c r="E183" s="42" t="n"/>
+    </row>
+    <row r="184" hidden="1" outlineLevel="1">
+      <c r="A184" s="42" t="n"/>
+      <c r="B184" s="42" t="inlineStr">
+        <is>
+          <t>챗봇 / REQ-078 음성 질문 입력 / 변경 · 최종 수정 · 비고</t>
+        </is>
+      </c>
+      <c r="C184" s="42" t="inlineStr">
+        <is>
+          <t>신규 · v1.0 · REQ-100(안내문 읽어주기)와 별개</t>
+        </is>
+      </c>
+      <c r="D184" s="42" t="inlineStr">
+        <is>
+          <t>수정 · v1.5 · 앱이 직접 녹음하지 않고 키보드의 받아쓰기 버튼을 쓰도록 안내 (10/6 수인 #50, 설계 메모 4-10) · REQ-100(안내문 읽어주기)와 별개</t>
+        </is>
+      </c>
+      <c r="E184" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -10330,7 +10388,7 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>사용자는 말로 질문을 입력할 수 있어야 하며, 인식에 실패하면 다시 말하기 또는 글자 입력을 선택할 수 있다.</t>
+          <t>사용자는 키보드 받아쓰기로 말로 질문을 입력할 수 있고, 처음 몇 번은 사용 방법을 안내받는다.</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -10340,7 +10398,7 @@
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>CB-05 · CB-05-E1</t>
+          <t>CB-05</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -10360,17 +10418,17 @@
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>수정</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
         <is>
-          <t>REQ-100(안내문 읽어주기)와 별개</t>
+          <t>앱이 직접 녹음하지 않고 키보드의 받아쓰기 버튼을 쓰도록 안내 (10/6 수인 #50, 설계 메모 4-10) · REQ-100(안내문 읽어주기)와 별개</t>
         </is>
       </c>
       <c r="N13" s="48" t="inlineStr">

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 규칙" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OCR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAG" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="챗봇" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실천·보상" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비기능" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="작성 규칙" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="요약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="공통" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="OCR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RAG" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="챗봇" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="실천·보상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="비기능" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'공통'!$A$4:$N$16</definedName>
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4546,13 +4546,227 @@
       </c>
       <c r="E184" s="42" t="n"/>
     </row>
+    <row r="185" ht="46" customHeight="1">
+      <c r="A185" s="39" t="inlineStr">
+        <is>
+          <t>v1.5 추가</t>
+        </is>
+      </c>
+      <c r="B185" s="39" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C185" s="40" t="inlineStr">
+        <is>
+          <t>건강 정보 받기(#101)와 별명 빼기(#96) 반영: REQ-001 가입 항목(흡연, 음주), REQ-005 동의 범위, REQ-006 내 정보 항목, REQ-004와 REQ-007 지워지는 목록에 건강 정보, REQ-045 비고(임부금기 다시 넣음)</t>
+        </is>
+      </c>
+      <c r="D185" s="43" t="n"/>
+      <c r="E185" s="39" t="inlineStr">
+        <is>
+          <t>이수인</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" hidden="1" outlineLevel="1">
+      <c r="A186" s="41" t="n"/>
+      <c r="B186" s="41" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="C186" s="41" t="inlineStr">
+        <is>
+          <t>현행 (As-Is)</t>
+        </is>
+      </c>
+      <c r="D186" s="41" t="inlineStr">
+        <is>
+          <t>개정 (To-Be)</t>
+        </is>
+      </c>
+      <c r="E186" s="41" t="n"/>
+    </row>
+    <row r="187" hidden="1" outlineLevel="1">
+      <c r="A187" s="42" t="n"/>
+      <c r="B187" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-001 회원가입 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C187" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 이메일과 비밀번호로 회원가입할 수 있어야 한다. 출생연도와 성별은 필수, 이름(별명)은 선택으로 입력한다.</t>
+        </is>
+      </c>
+      <c r="D187" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 이메일과 비밀번호로 회원가입할 수 있어야 한다. 출생연도, 성별, 흡연, 음주(최근 1년 빈도)는 필수로 입력하고, 흡연과 음주는 "잘 모르겠어요"를 고를 수 있다.</t>
+        </is>
+      </c>
+      <c r="E187" s="42" t="n"/>
+    </row>
+    <row r="188" hidden="1" outlineLevel="1">
+      <c r="A188" s="42" t="n"/>
+      <c r="B188" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-001 회원가입 / 최종 수정</t>
+        </is>
+      </c>
+      <c r="C188" s="42" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="D188" s="42" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="E188" s="42" t="n"/>
+    </row>
+    <row r="189" hidden="1" outlineLevel="1">
+      <c r="A189" s="42" t="n"/>
+      <c r="B189" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-004 회원 탈퇴 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C189" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 탈퇴 전 지워지는 정보 목록을 확인하고 동의해야 하며, 탈퇴 시 진료 정보 · 분석 결과 · 안내문 · 피드백 · 챗봇 대화 · 실천 목표 · 실천 기록 · 포인트 · 동의 기록이 즉시 삭제된다.</t>
+        </is>
+      </c>
+      <c r="D189" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 탈퇴 전 지워지는 정보 목록을 확인하고 동의해야 하며, 탈퇴 시 진료 정보 · 분석 결과 · 안내문 · 피드백 · 챗봇 대화 · 실천 목표 · 실천 기록 · 포인트 · 동의 기록과 건강 정보가 즉시 삭제된다.</t>
+        </is>
+      </c>
+      <c r="E189" s="42" t="n"/>
+    </row>
+    <row r="190" hidden="1" outlineLevel="1">
+      <c r="A190" s="42" t="n"/>
+      <c r="B190" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-005 개인정보 처리방침 동의 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C190" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 회원가입 시 민감정보(진료기록) 수집·이용에 대해 별도 동의해야 한다.</t>
+        </is>
+      </c>
+      <c r="D190" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 회원가입 시 민감정보(진료기록, 건강 정보) 수집·이용에 대해 별도 동의해야 한다.</t>
+        </is>
+      </c>
+      <c r="E190" s="42" t="n"/>
+    </row>
+    <row r="191" hidden="1" outlineLevel="1">
+      <c r="A191" s="42" t="n"/>
+      <c r="B191" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-005 개인정보 처리방침 동의 / 최종 수정</t>
+        </is>
+      </c>
+      <c r="C191" s="42" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="D191" s="42" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="E191" s="42" t="n"/>
+    </row>
+    <row r="192" hidden="1" outlineLevel="1">
+      <c r="A192" s="42" t="n"/>
+      <c r="B192" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-006 내 정보 조회 · 수정 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C192" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 이름(별명) · 출생연도 · 성별을 확인하고 수정할 수 있어야 한다. 이메일은 수정할 수 없고, 출생연도 · 성별 변경은 다음 분석부터 반영된다.</t>
+        </is>
+      </c>
+      <c r="D192" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 출생연도, 성별과 건강 정보(흡연, 음주, 질환, 임신(여성만), 투석, 키, 몸무게, 예정 검사)를 확인하고 수정할 수 있어야 한다. 이메일은 수정할 수 없고, 바뀐 정보는 다음 분석부터 반영된다.</t>
+        </is>
+      </c>
+      <c r="E192" s="42" t="n"/>
+    </row>
+    <row r="193" hidden="1" outlineLevel="1">
+      <c r="A193" s="42" t="n"/>
+      <c r="B193" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-006 내 정보 조회 · 수정 / 최종 수정</t>
+        </is>
+      </c>
+      <c r="C193" s="42" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="D193" s="42" t="inlineStr">
+        <is>
+          <t>v1.5</t>
+        </is>
+      </c>
+      <c r="E193" s="42" t="n"/>
+    </row>
+    <row r="194" hidden="1" outlineLevel="1">
+      <c r="A194" s="42" t="n"/>
+      <c r="B194" s="42" t="inlineStr">
+        <is>
+          <t>공통 / REQ-007 동의 내역 조회 · 철회 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C194" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 동의한 약관과 동의 일시를 확인하고 민감정보 수집 동의를 철회할 수 있어야 한다. 철회하면 업로드 · 분석을 이용할 수 없고, 처방전 · 분석 · 안내문 · 피드백 · 챗봇 대화는 삭제된다. 실천 목표는 종료하되 기록 · 포인트는 남긴다(질환 라벨은 지움).</t>
+        </is>
+      </c>
+      <c r="D194" s="42" t="inlineStr">
+        <is>
+          <t>사용자는 동의한 약관과 동의 일시를 확인하고 민감정보 수집 동의를 철회할 수 있어야 한다. 철회하면 업로드 · 분석을 이용할 수 없고, 처방전 · 분석 · 안내문 · 피드백 · 챗봇 대화와 건강 정보는 삭제된다. 실천 목표는 종료하되 기록 · 포인트는 남긴다(질환 라벨은 지움).</t>
+        </is>
+      </c>
+      <c r="E194" s="42" t="n"/>
+    </row>
+    <row r="195" hidden="1" outlineLevel="1">
+      <c r="A195" s="42" t="n"/>
+      <c r="B195" s="42" t="inlineStr">
+        <is>
+          <t>RAG / REQ-045 연령금기 점검 / 비고</t>
+        </is>
+      </c>
+      <c r="C195" s="42" t="inlineStr">
+        <is>
+          <t>임부금기 점검은 MVP 범위 밖 (10/2 팀 회의)</t>
+        </is>
+      </c>
+      <c r="D195" s="42" t="inlineStr">
+        <is>
+          <t>임부금기 점검은 내 정보에서 임신 여부를 받기로 하며 다시 넣음 (10/14 회의와 디코, 구현은 채연. 10/2 팀 회의에서는 MVP 범위 밖이었음)</t>
+        </is>
+      </c>
+      <c r="E195" s="42" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C91:D91"/>
     <mergeCell ref="C68:D68"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C65:D65"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C185:D185"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C127:D127"/>
     <mergeCell ref="C118:D118"/>
@@ -5087,6 +5301,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5182,7 +5397,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>사용자는 이메일과 비밀번호로 회원가입할 수 있어야 한다. 출생연도와 성별은 필수, 이름(별명)은 선택으로 입력한다.</t>
+          <t>사용자는 이메일과 비밀번호로 회원가입할 수 있어야 한다. 출생연도, 성별, 흡연, 음주(최근 1년 빈도)는 필수로 입력하고, 흡연과 음주는 "잘 모르겠어요"를 고를 수 있다.</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -5217,7 +5432,7 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
@@ -5326,7 +5541,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>사용자는 탈퇴 전 지워지는 정보 목록을 확인하고 동의해야 하며, 탈퇴 시 진료 정보 · 분석 결과 · 안내문 · 피드백 · 챗봇 대화 · 실천 목표 · 실천 기록 · 포인트 · 동의 기록이 즉시 삭제된다.</t>
+          <t>사용자는 탈퇴 전 지워지는 정보 목록을 확인하고 동의해야 하며, 탈퇴 시 진료 정보 · 분석 결과 · 안내문 · 피드백 · 챗봇 대화 · 실천 목표 · 실천 기록 · 포인트 · 동의 기록과 건강 정보가 즉시 삭제된다.</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -5398,7 +5613,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>사용자는 회원가입 시 민감정보(진료기록) 수집·이용에 대해 별도 동의해야 한다.</t>
+          <t>사용자는 회원가입 시 민감정보(진료기록, 건강 정보) 수집·이용에 대해 별도 동의해야 한다.</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -5433,7 +5648,7 @@
       </c>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="M8" s="18" t="inlineStr">
@@ -5470,7 +5685,7 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>사용자는 이름(별명) · 출생연도 · 성별을 확인하고 수정할 수 있어야 한다. 이메일은 수정할 수 없고, 출생연도 · 성별 변경은 다음 분석부터 반영된다.</t>
+          <t>사용자는 출생연도, 성별과 건강 정보(흡연, 음주, 질환, 임신(여성만), 투석, 키, 몸무게, 예정 검사)를 확인하고 수정할 수 있어야 한다. 이메일은 수정할 수 없고, 바뀐 정보는 다음 분석부터 반영된다.</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -5505,7 +5720,7 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
@@ -5542,7 +5757,7 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>사용자는 동의한 약관과 동의 일시를 확인하고 민감정보 수집 동의를 철회할 수 있어야 한다. 철회하면 업로드 · 분석을 이용할 수 없고, 처방전 · 분석 · 안내문 · 피드백 · 챗봇 대화는 삭제된다. 실천 목표는 종료하되 기록 · 포인트는 남긴다(질환 라벨은 지움).</t>
+          <t>사용자는 동의한 약관과 동의 일시를 확인하고 민감정보 수집 동의를 철회할 수 있어야 한다. 철회하면 업로드 · 분석을 이용할 수 없고, 처방전 · 분석 · 안내문 · 피드백 · 챗봇 대화와 건강 정보는 삭제된다. 실천 목표는 종료하되 기록 · 포인트는 남긴다(질환 라벨은 지움).</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -7583,6 +7798,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -8078,7 +8294,7 @@
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>임부금기 점검은 MVP 범위 밖 (10/2 팀 회의)</t>
+          <t>임부금기 점검은 내 정보에서 임신 여부를 받기로 하며 다시 넣음 (10/14 회의와 디코, 구현은 채연. 10/2 팀 회의에서는 MVP 범위 밖이었음)</t>
         </is>
       </c>
       <c r="N10" s="44" t="inlineStr">

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -5301,7 +5301,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7798,7 +7797,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -774,6 +774,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -4559,7 +4560,7 @@
       </c>
       <c r="C185" s="40" t="inlineStr">
         <is>
-          <t>건강 정보 받기(#101)와 별명 빼기(#96) 반영: REQ-001 가입 항목(흡연, 음주), REQ-005 동의 범위, REQ-006 내 정보 항목, REQ-004와 REQ-007 지워지는 목록에 건강 정보, REQ-045 비고(임부금기 다시 넣음)</t>
+          <t>건강 정보 받기(#101)와 별명 빼기(#96) 반영: REQ-001 가입 항목(흡연, 음주), REQ-005 동의 범위, REQ-006 내 정보 항목, REQ-004와 REQ-007 지워지는 목록에 건강 정보, REQ-045 비고(임신 여부를 받기로 함)</t>
         </is>
       </c>
       <c r="D185" s="43" t="n"/>
@@ -4754,7 +4755,7 @@
       </c>
       <c r="D195" s="42" t="inlineStr">
         <is>
-          <t>임부금기 점검은 내 정보에서 임신 여부를 받기로 하며 다시 넣음 (10/14 회의와 디코, 구현은 채연. 10/2 팀 회의에서는 MVP 범위 밖이었음)</t>
+          <t>내 정보에서 여성에게 임신 여부를 받기로 함 (10/14 회의와 디코). 임부금기 점검을 넣을지는 정하지 않음 (#101). 10/2 팀 회의에서는 MVP 범위 밖</t>
         </is>
       </c>
       <c r="E195" s="42" t="n"/>
@@ -4813,6 +4814,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5202,6 +5204,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -5301,6 +5304,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6295,6 +6299,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7797,6 +7802,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -8292,7 +8298,7 @@
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>임부금기 점검은 내 정보에서 임신 여부를 받기로 하며 다시 넣음 (10/14 회의와 디코, 구현은 채연. 10/2 팀 회의에서는 MVP 범위 밖이었음)</t>
+          <t>내 정보에서 여성에게 임신 여부를 받기로 함 (10/14 회의와 디코). 임부금기 점검을 넣을지는 정하지 않음 (#101). 10/2 팀 회의에서는 MVP 범위 밖</t>
         </is>
       </c>
       <c r="N10" s="44" t="inlineStr">
@@ -9935,6 +9941,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -11145,6 +11152,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -11855,6 +11863,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -774,7 +774,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -918,7 +917,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4759,6 +4758,25 @@
         </is>
       </c>
       <c r="E195" s="42" t="n"/>
+    </row>
+    <row r="196" outlineLevel="1">
+      <c r="A196" s="42" t="n"/>
+      <c r="B196" s="42" t="inlineStr">
+        <is>
+          <t>RAG / REQ-060 질환별 생활습관 가이드 / 비고</t>
+        </is>
+      </c>
+      <c r="C196" s="42" t="inlineStr">
+        <is>
+          <t>참여기업 필수 요구사항</t>
+        </is>
+      </c>
+      <c r="D196" s="42" t="inlineStr">
+        <is>
+          <t>참여기업 필수 요구사항. 상병코드는 처방전 질환과 내 정보 질환을 합쳐 씀 (10/19 합의, #101)</t>
+        </is>
+      </c>
+      <c r="E196" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4814,7 +4832,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5204,7 +5221,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -5304,7 +5320,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6299,7 +6314,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7802,7 +7816,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9298,7 +9311,7 @@
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>참여기업 필수 요구사항</t>
+          <t>참여기업 필수 요구사항. 상병코드는 처방전 질환과 내 정보 질환을 합쳐 씀 (10/19 합의, #101)</t>
         </is>
       </c>
       <c r="N24" s="44" t="inlineStr">
@@ -9941,7 +9954,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -11152,7 +11164,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -11863,7 +11874,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="작성 규칙" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="요약" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="공통" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="OCR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RAG" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="챗봇" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="실천·보상" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="비기능" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 규칙" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경 이력" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OCR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAG" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="챗봇" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실천·보상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비기능" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'공통'!$A$4:$N$16</definedName>
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4777,6 +4777,44 @@
         </is>
       </c>
       <c r="E196" s="42" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="42" t="n"/>
+      <c r="B197" s="42" t="inlineStr">
+        <is>
+          <t>RAG / REQ-057 확인된 위험 없음 안내 / 요구사항명</t>
+        </is>
+      </c>
+      <c r="C197" s="42" t="inlineStr">
+        <is>
+          <t>확인된 위험 없음 안내</t>
+        </is>
+      </c>
+      <c r="D197" s="42" t="inlineStr">
+        <is>
+          <t>걸린 항목 없음 안내</t>
+        </is>
+      </c>
+      <c r="E197" s="42" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="42" t="n"/>
+      <c r="B198" s="42" t="inlineStr">
+        <is>
+          <t>RAG / REQ-057 확인된 위험 없음 안내 / 상세 내용</t>
+        </is>
+      </c>
+      <c r="C198" s="42" t="inlineStr">
+        <is>
+          <t>시스템은 경고가 0건일 때 "안전하다"고 단정하지 않고 "확인된 위험이 없다"는 문구, 점검한 항목 목록, 자료의 한계를 함께 보여줘야 한다.</t>
+        </is>
+      </c>
+      <c r="D198" s="42" t="inlineStr">
+        <is>
+          <t>시스템은 경고가 0건일 때 "안전하다"고 단정하지 않고 "점검 기준에서 걸린 항목이 없다"는 문구, 점검한 항목 목록, 자료의 한계를 함께 보여줘야 한다. (10/22 문구 변경: "안전하다"로 읽힐 수 있어 점검 범위를 그대로 알리는 문구로 바꿈)</t>
+        </is>
+      </c>
+      <c r="E198" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -9122,12 +9160,12 @@
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>확인된 위험 없음 안내</t>
+          <t>걸린 항목 없음 안내</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>시스템은 경고가 0건일 때 "안전하다"고 단정하지 않고 "확인된 위험이 없다"는 문구, 점검한 항목 목록, 자료의 한계를 함께 보여줘야 한다.</t>
+          <t>시스템은 경고가 0건일 때 "안전하다"고 단정하지 않고 "점검 기준에서 걸린 항목이 없다"는 문구, 점검한 항목 목록, 자료의 한계를 함께 보여줘야 한다.</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">

--- a/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.5.xlsx
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4815,6 +4815,26 @@
         </is>
       </c>
       <c r="E198" s="42" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="42" t="n"/>
+      <c r="B199" s="42" t="inlineStr">
+        <is>
+          <t>실천·보상 / 탭 설명 (2행)과 요약 / 실천·보상 담당 · 범위</t>
+        </is>
+      </c>
+      <c r="C199" s="42" t="inlineStr">
+        <is>
+          <t>채연 (화면 수인) · 추천 · 목표 · 실천 기록 · 포인트</t>
+        </is>
+      </c>
+      <c r="D199" s="42" t="inlineStr">
+        <is>
+          <t>서버 수인(#155) 이어서 채연 · 화면 채연 · 추천 · 목표 · 실천 기록 · 포인트
+사유: 실천 서버(P-1 ~ P-4)를 수인이 먼저 만들어 #155로 머지하고, 실천 탭 앱 화면은 채연이 만들기로 함 (10/30 회의, #155 머지 10/31). REQ-110 ~ 117 행의 담당 칸(채연)은 그대로</t>
+        </is>
+      </c>
+      <c r="E199" s="42" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5127,7 +5147,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>채연 (화면 수인) · 추천 · 목표 · 실천 기록 · 포인트</t>
+          <t>서버 수인(#155) 이어서 채연 · 화면 채연 · 추천 · 목표 · 실천 기록 · 포인트</t>
         </is>
       </c>
       <c r="C9" s="6">
@@ -11198,7 +11218,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>채연 (화면 수인) · 추천 · 목표 · 실천 기록 · 포인트 · 관련 화면 RW · 행을 바꾸면 "변경 이력" 탭에 한 줄 추가</t>
+          <t>서버 수인(#155) 이어서 채연 · 화면 채연 · 추천 · 목표 · 실천 기록 · 포인트 · 관련 화면 RW · 행을 바꾸면 "변경 이력" 탭에 한 줄 추가</t>
         </is>
       </c>
     </row>
